--- a/instrumentos/excel/DAIR_Checklist_Operacional_v0.3.xlsx
+++ b/instrumentos/excel/DAIR_Checklist_Operacional_v0.3.xlsx
@@ -281,13 +281,13 @@
     <t xml:space="preserve">Evento registrado na linha do tempo (Instrumento 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify &amp; Triage</t>
+    <t xml:space="preserve">Verify and Triage</t>
   </si>
   <si>
     <t xml:space="preserve">Confirmar a natureza do incidente</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmar se há comprometimento de confidencialidade, integridade, disponibilidade ou autenticidade de dados pessoais — mesmo sem atacante identificado, sem exportação de dados ou sem indício de acesso indevido (ex.: indisponibilidade por falha técnica, ou alteração indevida de dados sem exfiltração)</t>
+    <t xml:space="preserve">Confirmar se há comprometimento de confidencialidade, integridade, disponibilidade ou autenticidade de dados pessoais, qualquer que seja a causa — maliciosa, acidental ou ambiental (ex.: falha de infraestrutura, energia ou de provedor de nuvem) — mesmo sem atacante identificado, sem exportação de dados ou sem indício de acesso indevido (ex.: indisponibilidade por falha técnica ou ambiental, ou alteração indevida de dados sem exfiltração)</t>
   </si>
   <si>
     <t xml:space="preserve">Logs e evidências preliminares disponíveis</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">Evidência de confirmação da natureza do incidente</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmação registrada com grau de certeza explícito, indicando qual(is) dimensão(ões) — confidencialidade, integridade, disponibilidade, autenticidade — foram afetadas</t>
+    <t xml:space="preserve">Confirmação registrada com grau de certeza explícito, indicando qual(is) dimensão(ões) — confidencialidade, integridade, disponibilidade, autenticidade — e qual causa (maliciosa, acidental ou ambiental) foram identificadas</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="R6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="9" t="s">
@@ -5614,7 +5614,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B24" type="list">
@@ -5642,7 +5642,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B25" type="list">
@@ -5670,7 +5670,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B26" type="list">
@@ -5698,7 +5698,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27" type="list">
@@ -5726,7 +5726,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B28" type="list">
@@ -5754,7 +5754,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B29" type="list">
@@ -5782,7 +5782,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B30" type="list">
@@ -5810,7 +5810,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B31" type="list">
@@ -5838,7 +5838,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B32" type="list">
@@ -5866,7 +5866,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B33" type="list">
@@ -5894,7 +5894,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B34" type="list">
@@ -5922,7 +5922,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B35" type="list">
@@ -5950,7 +5950,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B36" type="list">
@@ -5978,7 +5978,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B37" type="list">
@@ -6006,7 +6006,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C38" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B38" type="list">
@@ -6034,7 +6034,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C39" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B39" type="list">
@@ -6062,7 +6062,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C40" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B40" type="list">
@@ -6090,7 +6090,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B41" type="list">
@@ -6118,7 +6118,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C42" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B42" type="list">
@@ -6146,7 +6146,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C43" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B43" type="list">
@@ -6174,7 +6174,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C44" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B44" type="list">
@@ -6202,7 +6202,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C45" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B45" type="list">
@@ -6230,7 +6230,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C46" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B46" type="list">
@@ -6258,7 +6258,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C47" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B47" type="list">
@@ -6286,7 +6286,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C48" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B48" type="list">
@@ -6314,7 +6314,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C49" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B49" type="list">
@@ -6342,7 +6342,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C50" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B50" type="list">
@@ -6370,7 +6370,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C51" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B51" type="list">
@@ -6398,7 +6398,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C52" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B52" type="list">
@@ -6426,7 +6426,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C53" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B53" type="list">
@@ -6454,7 +6454,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C54" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B54" type="list">
@@ -6482,7 +6482,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C55" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B55" type="list">
@@ -6510,7 +6510,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C56" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B56" type="list">
@@ -6538,7 +6538,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C57" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B57" type="list">
@@ -6566,7 +6566,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C58" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B58" type="list">
@@ -6594,7 +6594,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C59" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B59" type="list">
@@ -6622,7 +6622,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B60" type="list">
@@ -6650,7 +6650,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C61" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B61" type="list">
@@ -6678,7 +6678,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C62" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B62" type="list">
@@ -6706,7 +6706,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C63" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B63" type="list">
@@ -6734,7 +6734,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C64" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B64" type="list">
@@ -6762,7 +6762,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C65" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B65" type="list">
@@ -6790,7 +6790,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C66" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B66" type="list">
@@ -6818,7 +6818,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C67" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B67" type="list">
@@ -6846,7 +6846,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C68" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B68" type="list">
@@ -6874,7 +6874,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C69" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B69" type="list">
@@ -6902,7 +6902,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C70" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B70" type="list">
@@ -6930,7 +6930,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C71" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B71" type="list">
@@ -6958,7 +6958,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C72" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B72" type="list">
@@ -6986,7 +6986,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C73" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B73" type="list">
@@ -7014,7 +7014,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C74" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B74" type="list">
@@ -7042,7 +7042,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C75" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B75" type="list">
@@ -7070,7 +7070,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C76" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B76" type="list">
@@ -7098,7 +7098,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C77" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B77" type="list">
@@ -7126,7 +7126,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C78" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B78" type="list">
@@ -7154,7 +7154,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C79" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B79" type="list">
@@ -7182,7 +7182,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C80" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B80" type="list">
@@ -7210,7 +7210,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C81" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B81" type="list">
@@ -7238,7 +7238,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C82" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B82" type="list">
@@ -7266,7 +7266,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C83" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B83" type="list">
@@ -7294,7 +7294,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C84" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B84" type="list">
@@ -7322,7 +7322,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C85" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B85" type="list">
@@ -7350,7 +7350,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C86" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B86" type="list">
@@ -7378,7 +7378,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C87" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B87" type="list">
@@ -7406,7 +7406,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C88" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B88" type="list">
@@ -7434,7 +7434,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C89" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B89" type="list">
@@ -7462,7 +7462,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C90" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B90" type="list">
@@ -7490,7 +7490,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C91" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B91" type="list">
@@ -7518,7 +7518,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C92" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B92" type="list">
@@ -7546,7 +7546,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C93" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B93" type="list">
@@ -7574,7 +7574,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C94" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B94" type="list">
@@ -7602,7 +7602,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C95" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B95" type="list">
@@ -7630,7 +7630,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C96" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B96" type="list">
@@ -7658,7 +7658,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C97" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B97" type="list">
@@ -7686,7 +7686,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C98" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B98" type="list">
@@ -7714,7 +7714,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C99" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B99" type="list">
@@ -7742,7 +7742,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C100" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B100" type="list">
@@ -7770,7 +7770,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C101" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B101" type="list">
@@ -7798,7 +7798,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C102" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B102" type="list">
@@ -7826,7 +7826,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C103" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B103" type="list">
@@ -7854,7 +7854,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C104" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B104" type="list">
@@ -7882,7 +7882,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C105" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B105" type="list">
@@ -7910,7 +7910,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C106" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B106" type="list">
@@ -7938,7 +7938,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C107" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B107" type="list">
@@ -7966,7 +7966,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C108" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B108" type="list">
@@ -7994,7 +7994,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C109" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B109" type="list">
@@ -8022,7 +8022,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C110" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B110" type="list">
@@ -8050,7 +8050,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C111" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B111" type="list">
@@ -8078,7 +8078,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C112" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B112" type="list">
@@ -8106,7 +8106,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C113" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B113" type="list">
@@ -8134,7 +8134,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C114" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B114" type="list">
@@ -8162,7 +8162,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C115" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B115" type="list">
@@ -8190,7 +8190,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C116" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B116" type="list">
@@ -8218,7 +8218,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C117" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B117" type="list">
@@ -8246,7 +8246,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C118" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B118" type="list">
@@ -8274,7 +8274,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C119" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B119" type="list">
@@ -8302,7 +8302,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C120" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B120" type="list">
@@ -8330,7 +8330,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C121" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B121" type="list">
@@ -8358,7 +8358,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C122" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B122" type="list">
@@ -8386,7 +8386,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C123" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B123" type="list">
@@ -8414,7 +8414,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C124" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B124" type="list">
@@ -8442,7 +8442,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C125" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B125" type="list">
@@ -8470,7 +8470,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C126" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B126" type="list">
@@ -8498,7 +8498,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C127" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B127" type="list">
@@ -8526,7 +8526,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C128" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B128" type="list">
@@ -8554,7 +8554,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C129" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B129" type="list">
@@ -8582,7 +8582,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C130" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B130" type="list">
@@ -8610,7 +8610,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C131" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B131" type="list">
@@ -8638,7 +8638,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C132" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B132" type="list">
@@ -8666,7 +8666,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C133" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B133" type="list">
@@ -8694,7 +8694,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C134" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B134" type="list">
@@ -8722,7 +8722,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C135" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B135" type="list">
@@ -8750,7 +8750,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C136" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B136" type="list">
@@ -8778,7 +8778,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C137" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B137" type="list">
@@ -8806,7 +8806,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C138" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B138" type="list">
@@ -8834,7 +8834,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C139" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B139" type="list">
@@ -8862,7 +8862,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C140" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B140" type="list">
@@ -8890,7 +8890,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C141" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B141" type="list">
@@ -8918,7 +8918,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C142" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B142" type="list">
@@ -8946,7 +8946,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C143" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B143" type="list">
@@ -8974,7 +8974,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C144" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B144" type="list">
@@ -9002,7 +9002,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C145" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B145" type="list">
@@ -9030,7 +9030,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C146" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B146" type="list">
@@ -9058,7 +9058,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C147" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B147" type="list">
@@ -9086,7 +9086,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C148" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B148" type="list">
@@ -9114,7 +9114,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C149" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B149" type="list">
@@ -9142,7 +9142,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C150" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B150" type="list">
@@ -9170,7 +9170,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C151" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B151" type="list">
@@ -9198,7 +9198,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C152" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B152" type="list">
@@ -9226,7 +9226,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C153" type="list">
-      <formula1>"Prepare,Detect,Verify &amp; Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
+      <formula1>"Prepare,Detect,Verify and Triage,Scope,Contain,Eradicate,Recover,Debrief"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B153" type="list">

--- a/instrumentos/excel/DAIR_Checklist_Operacional_v0.3.xlsx
+++ b/instrumentos/excel/DAIR_Checklist_Operacional_v0.3.xlsx
@@ -35,7 +35,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02. Padrão CIC-NN. O DAIR original exige decisão explícita e atribuível (coluna 'Decisão de Saída') para encerrar cada iteração do loop — nunca encerre apenas por decurso de tempo.</t>
+          <t xml:space="preserve">ID manual e estável: A02. Padrão CIC-NN. O DAIR original exige decisão explícita e atribuível (coluna 'Decisão de Saída') para encerrar cada iteração do loop: nunca encerre apenas por decurso de tempo.</t>
         </r>
       </text>
     </comment>
@@ -57,7 +57,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">ID manual e estável — A02. Padrão CHK-NNN.</t>
+          <t xml:space="preserve">ID manual e estável: A02. Padrão CHK-NNN.</t>
         </r>
       </text>
     </comment>
@@ -69,7 +69,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Vincule o ID da ação correspondente no Plano de Ações do Instrumento 1 (ACA-NNN) sempre que esta atividade tiver uma ação de resposta ou corretiva registrada lá — a ligação não é automática (A12).</t>
+          <t xml:space="preserve">Vincule o ID da ação correspondente no Plano de Ações do Instrumento 1 (ACA-NNN) sempre que esta atividade tiver uma ação de resposta ou corretiva registrada lá: a ligação não é automática (A12).</t>
         </r>
       </text>
     </comment>
@@ -80,7 +80,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="158">
   <si>
-    <t xml:space="preserve">DAIR — Checklist Operacional Dinâmico</t>
+    <t xml:space="preserve">DAIR: Checklist Operacional Dinâmico</t>
   </si>
   <si>
     <t xml:space="preserve">Versão 0.3 · Instrumento 3 de 5 · Modelo reutilizável</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">O que é este arquivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Checklist para uso durante a execução de um incidente, organizado por atividade — não por uma sequência fixa de fases. Cobre os oito waypoints do DAIR, com ênfase nas atividades do Response Actions Loop (Scope, Contain, Eradicate, Recover), que podem se repetir em múltiplas iterações.</t>
+    <t xml:space="preserve">Checklist para uso durante a execução de um incidente, organizado por atividade: não por uma sequência fixa de fases. Cobre os oito waypoints do DAIR, com ênfase nas atividades do Response Actions Loop (Scope, Contain, Eradicate, Recover), que podem se repetir em múltiplas iterações.</t>
   </si>
   <si>
     <t xml:space="preserve">Este checklist NÃO é linear</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">Conclusão de atividade x efetividade comprovada</t>
   </si>
   <si>
-    <t xml:space="preserve">A coluna 'Status' indica se a atividade foi executada. A coluna 'Efetividade Comprovada' é independente e indica se há validação técnica de que a medida funcionou (por exemplo: a atividade 'revogar token' pode estar com Status = Concluída e Efetividade = Testada — inefetiva, caso se descubra posteriormente que o token continuava ativo). Nunca presuma efetividade apenas porque a atividade foi marcada como concluída.</t>
+    <t xml:space="preserve">A coluna 'Status' indica se a atividade foi executada. A coluna 'Efetividade Comprovada' é independente e indica se há validação técnica de que a medida funcionou (por exemplo: a atividade 'revogar token' pode estar com Status = Concluída e Efetividade = Testada: inefetiva, caso se descubra posteriormente que o token continuava ativo). Nunca presuma efetividade apenas porque a atividade foi marcada como concluída.</t>
   </si>
   <si>
     <t xml:space="preserve">Camada de privacidade transversal</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">Controle de ciclos</t>
   </si>
   <si>
-    <t xml:space="preserve">A aba Controle_Ciclos registra a abertura e o encerramento de cada iteração do Response Actions Loop, o evento que motivou a reentrada e a decisão (ID) que autorizou a saída do ciclo — conforme o modelo DAIR original, que exige decisão explícita e atribuível para encerrar o loop.</t>
+    <t xml:space="preserve">A aba Controle_Ciclos registra a abertura e o encerramento de cada iteração do Response Actions Loop, o evento que motivou a reentrada e a decisão (ID) que autorizou a saída do ciclo: conforme o modelo DAIR original, que exige decisão explícita e atribuível para encerrar o loop.</t>
   </si>
   <si>
     <t xml:space="preserve">Linhas pré-preenchidas</t>
   </si>
   <si>
-    <t xml:space="preserve">As colunas Waypoint, Objetivo, Atividade, Condição de Execução, Evidência Exigida, Critério de Conclusão e Impacto em Privacidade trazem um catálogo genérico de atividades recorrentes em incidentes com dados pessoais, incluindo as verificações específicas exigidas (revogação de identidades/sessões/tokens, persistência do atacante, validação de contenção, reavaliação de escopo, preservação de evidências, recuperação de serviços, riscos residuais e debrief). Ajuste, remova ou acrescente linhas conforme a realidade da sua organização — nenhuma delas deve ser lida como dado de um incidente real.</t>
+    <t xml:space="preserve">As colunas Waypoint, Objetivo, Atividade, Condição de Execução, Evidência Exigida, Critério de Conclusão e Impacto em Privacidade trazem um catálogo genérico de atividades recorrentes em incidentes com dados pessoais, incluindo as verificações específicas exigidas (revogação de identidades/sessões/tokens, persistência do atacante, validação de contenção, reavaliação de escopo, preservação de evidências, recuperação de serviços, riscos residuais e debrief). Ajuste, remova ou acrescente linhas conforme a realidade da sua organização: nenhuma delas deve ser lida como dado de um incidente real.</t>
   </si>
   <si>
     <t xml:space="preserve">Campos de entrada</t>
   </si>
   <si>
-    <t xml:space="preserve">Preencha Responsável, Prazo/Data, Status, Efetividade Comprovada, Resultado Observado, Evidência Vinculada, Ação Vinculada no Plano de Ações e Necessidade de Revisão durante a resposta. Deixe 'Não iniciada' / 'Não testada' quando ainda não houver informação — não deixe células em branco sem explicação.</t>
+    <t xml:space="preserve">Preencha Responsável, Prazo/Data, Status, Efetividade Comprovada, Resultado Observado, Evidência Vinculada, Ação Vinculada no Plano de Ações e Necessidade de Revisão durante a resposta. Deixe 'Não iniciada' / 'Não testada' quando ainda não houver informação: não deixe células em branco sem explicação.</t>
   </si>
   <si>
     <t xml:space="preserve">Identificadores manuais (A02)</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">O que a proteção de células NÃO garante</t>
   </si>
   <si>
-    <t xml:space="preserve">O destaque de células é um controle de usabilidade, não um controle de segurança da informação — a proteção de acesso ao arquivo preenchido é responsabilidade da organização (A11).</t>
+    <t xml:space="preserve">O destaque de células é um controle de usabilidade, não um controle de segurança da informação: a proteção de acesso ao arquivo preenchido é responsabilidade da organização (A11).</t>
   </si>
   <si>
     <t xml:space="preserve">Controle de Ciclos DAIR</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">Checklist Operacional Dinâmico</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordem livre. Use Ciclo DAIR para distinguir iterações. Catálogo genérico — ajuste à sua organização.</t>
+    <t xml:space="preserve">Ordem livre. Use Ciclo DAIR para distinguir iterações. Catálogo genérico: ajuste à sua organização.</t>
   </si>
   <si>
     <t xml:space="preserve">ID da Atividade</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Evidência Vinculada (ID)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ação Vinculada no Plano de Ações (ID ACA- — obrigatório quando houver ação correspondente no Instrumento 1)</t>
+    <t xml:space="preserve">Ação Vinculada no Plano de Ações (ID ACA-: obrigatório quando houver ação correspondente no Instrumento 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Resultado Observado</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">Identificar o evento inicial</t>
   </si>
   <si>
-    <t xml:space="preserve">Registrar o alerta ou indício inicial, preservando horário, fonte e timezone. A detecção pode vir de ferramenta de monitoramento, de relato de pessoas (funcionários, titulares) ou de terceiros/fornecedores — nenhuma dessas origens é pré-requisito das demais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indício de qualquer origem (ferramenta, pessoa ou fornecedor) — não depende de haver ferramenta de monitoramento</t>
+    <t xml:space="preserve">Registrar o alerta ou indício inicial, preservando horário, fonte e timezone. A detecção pode vir de ferramenta de monitoramento, de relato de pessoas (funcionários, titulares) ou de terceiros/fornecedores: nenhuma dessas origens é pré-requisito das demais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indício de qualquer origem (ferramenta, pessoa ou fornecedor): não depende de haver ferramenta de monitoramento</t>
   </si>
   <si>
     <t xml:space="preserve">Registro bruto do alerta ou relato preservado</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">Confirmar a natureza do incidente</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmar se há comprometimento de confidencialidade, integridade, disponibilidade ou autenticidade de dados pessoais, qualquer que seja a causa — maliciosa, acidental ou ambiental (ex.: falha de infraestrutura, energia ou de provedor de nuvem) — mesmo sem atacante identificado, sem exportação de dados ou sem indício de acesso indevido (ex.: indisponibilidade por falha técnica ou ambiental, ou alteração indevida de dados sem exfiltração)</t>
+    <t xml:space="preserve">Confirmar se há comprometimento de confidencialidade, integridade, disponibilidade ou autenticidade de dados pessoais, qualquer que seja a causa: maliciosa, acidental ou ambiental (ex.: falha de infraestrutura, energia ou de provedor de nuvem), mesmo sem atacante identificado, sem exportação de dados ou sem indício de acesso indevido (ex.: indisponibilidade por falha técnica ou ambiental, ou alteração indevida de dados sem exfiltração)</t>
   </si>
   <si>
     <t xml:space="preserve">Logs e evidências preliminares disponíveis</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">Evidência de confirmação da natureza do incidente</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmação registrada com grau de certeza explícito, indicando qual(is) dimensão(ões) — confidencialidade, integridade, disponibilidade, autenticidade — e qual causa (maliciosa, acidental ou ambiental) foram identificadas</t>
+    <t xml:space="preserve">Confirmação registrada com grau de certeza explícito, indicando qual(is) dimensão(ões) (confidencialidade, integridade, disponibilidade, autenticidade) e qual causa (maliciosa, acidental ou ambiental) foram identificadas</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
@@ -699,44 +699,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1004,91 +1008,91 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1115,418 +1119,418 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="7"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="7"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="7"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="7"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="7"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="7"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="7"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="7"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="7"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="7"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="7"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="7"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="7"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="7"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="7"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="7"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="7"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="7"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="7"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="7"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="7"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="7"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="7"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="7"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="7"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="7"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="7"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="7"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="7"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="7"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="7"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="7"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="7"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="7"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="7"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1699,7 +1703,7 @@
       <formula1>"Aberto,Encerrado,Reaberto"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: CIC-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão CIC-01. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A43" type="custom">
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: CIC-01." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão CIC-01. Não é gerado automaticamente; preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A43" type="custom">
       <formula1>OR(A4="",COUNTIF($A$4:$A$43,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1723,3404 +1727,3404 @@
   <dimension ref="A1:R153"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="9" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="9" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="9" t="s">
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="R4" s="7"/>
+      <c r="R4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="9" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="9" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="9" t="s">
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="R5" s="7"/>
+      <c r="R5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="9" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="9" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="9" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="R6" s="7"/>
+      <c r="R6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="9" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="9" t="s">
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="9" t="s">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="Q7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R7" s="7"/>
+      <c r="R7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="9" t="s">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="9" t="s">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="7"/>
+      <c r="R8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="9" t="s">
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="9" t="s">
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="Q9" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R9" s="7"/>
+      <c r="R9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="9" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="9" t="s">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R10" s="7"/>
+      <c r="R10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="9" t="s">
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="9" t="s">
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R11" s="7"/>
+      <c r="R11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="9" t="s">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="9" t="s">
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R12" s="7"/>
+      <c r="R12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="9" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9" t="s">
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="9" t="s">
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R13" s="7"/>
+      <c r="R13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="9" t="s">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="9" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="9" t="s">
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="Q14" s="9" t="s">
+      <c r="Q14" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R14" s="7"/>
+      <c r="R14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="9" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="9" t="s">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="9" t="s">
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="Q15" s="9" t="s">
+      <c r="Q15" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="R15" s="7"/>
+      <c r="R15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="9" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="9" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="9" t="s">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="Q16" s="9" t="s">
+      <c r="Q16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R16" s="7"/>
+      <c r="R16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="9" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="9" t="s">
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="9" t="s">
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="9" t="s">
+      <c r="Q17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="R17" s="7"/>
+      <c r="R17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="9" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="9" t="s">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="9" t="s">
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="Q18" s="9" t="s">
+      <c r="Q18" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R18" s="7"/>
+      <c r="R18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="9" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="9" t="s">
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="9" t="s">
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="Q19" s="9" t="s">
+      <c r="Q19" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="R19" s="7"/>
+      <c r="R19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="9" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="9" t="s">
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="9" t="s">
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="Q20" s="9" t="s">
+      <c r="Q20" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R20" s="7"/>
+      <c r="R20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="9" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="9" t="s">
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="9" t="s">
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="Q21" s="9" t="s">
+      <c r="Q21" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="R21" s="7"/>
+      <c r="R21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="9" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="9" t="s">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="9" t="s">
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="Q22" s="9" t="s">
+      <c r="Q22" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R22" s="7"/>
+      <c r="R22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="9" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="9" t="s">
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="9" t="s">
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="Q23" s="9" t="s">
+      <c r="Q23" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="R23" s="7"/>
+      <c r="R23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="8"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="7"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="7"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="8"/>
+      <c r="R43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="7"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
+      <c r="Q49" s="8"/>
+      <c r="R49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
-      <c r="R53" s="7"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="8"/>
+      <c r="R53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="8"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
-      <c r="R55" s="7"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="N56" s="7"/>
-      <c r="O56" s="7"/>
-      <c r="P56" s="7"/>
-      <c r="Q56" s="7"/>
-      <c r="R56" s="7"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="8"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="7"/>
-      <c r="O57" s="7"/>
-      <c r="P57" s="7"/>
-      <c r="Q57" s="7"/>
-      <c r="R57" s="7"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="8"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="7"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="8"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="8"/>
+      <c r="R59" s="8"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="7"/>
-      <c r="R60" s="7"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
+      <c r="Q60" s="8"/>
+      <c r="R60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
-      <c r="N61" s="7"/>
-      <c r="O61" s="7"/>
-      <c r="P61" s="7"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="7"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="8"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="7"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="8"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
-      <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="7"/>
-      <c r="Q63" s="7"/>
-      <c r="R63" s="7"/>
+      <c r="A63" s="7"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="N63" s="8"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
+      <c r="Q63" s="8"/>
+      <c r="R63" s="8"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="7"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="8"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
+      <c r="Q64" s="8"/>
+      <c r="R64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
-      <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="7"/>
-      <c r="Q65" s="7"/>
-      <c r="R65" s="7"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="N65" s="8"/>
+      <c r="O65" s="8"/>
+      <c r="P65" s="8"/>
+      <c r="Q65" s="8"/>
+      <c r="R65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="7"/>
-      <c r="Q66" s="7"/>
-      <c r="R66" s="7"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="8"/>
+      <c r="N66" s="8"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
+      <c r="Q66" s="8"/>
+      <c r="R66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
-      <c r="N67" s="7"/>
-      <c r="O67" s="7"/>
-      <c r="P67" s="7"/>
-      <c r="Q67" s="7"/>
-      <c r="R67" s="7"/>
+      <c r="A67" s="7"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
+      <c r="Q67" s="8"/>
+      <c r="R67" s="8"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
-      <c r="Q68" s="7"/>
-      <c r="R68" s="7"/>
+      <c r="A68" s="7"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="N68" s="8"/>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8"/>
+      <c r="Q68" s="8"/>
+      <c r="R68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="7"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="8"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
+      <c r="Q69" s="8"/>
+      <c r="R69" s="8"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="7"/>
-      <c r="R70" s="7"/>
+      <c r="A70" s="7"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8"/>
+      <c r="Q70" s="8"/>
+      <c r="R70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
-      <c r="M71" s="7"/>
-      <c r="N71" s="7"/>
-      <c r="O71" s="7"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
-      <c r="R71" s="7"/>
+      <c r="A71" s="7"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="8"/>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8"/>
+      <c r="Q71" s="8"/>
+      <c r="R71" s="8"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="7"/>
-      <c r="O72" s="7"/>
-      <c r="P72" s="7"/>
-      <c r="Q72" s="7"/>
-      <c r="R72" s="7"/>
+      <c r="A72" s="7"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="N72" s="8"/>
+      <c r="O72" s="8"/>
+      <c r="P72" s="8"/>
+      <c r="Q72" s="8"/>
+      <c r="R72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="7"/>
-      <c r="Q73" s="7"/>
-      <c r="R73" s="7"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+      <c r="N73" s="8"/>
+      <c r="O73" s="8"/>
+      <c r="P73" s="8"/>
+      <c r="Q73" s="8"/>
+      <c r="R73" s="8"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="7"/>
+      <c r="A74" s="7"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="8"/>
+      <c r="O74" s="8"/>
+      <c r="P74" s="8"/>
+      <c r="Q74" s="8"/>
+      <c r="R74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
-      <c r="R75" s="7"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+      <c r="N75" s="8"/>
+      <c r="O75" s="8"/>
+      <c r="P75" s="8"/>
+      <c r="Q75" s="8"/>
+      <c r="R75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="7"/>
-      <c r="R76" s="7"/>
+      <c r="A76" s="7"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+      <c r="N76" s="8"/>
+      <c r="O76" s="8"/>
+      <c r="P76" s="8"/>
+      <c r="Q76" s="8"/>
+      <c r="R76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
-      <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="7"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+      <c r="N77" s="8"/>
+      <c r="O77" s="8"/>
+      <c r="P77" s="8"/>
+      <c r="Q77" s="8"/>
+      <c r="R77" s="8"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
-      <c r="O78" s="7"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="7"/>
-      <c r="R78" s="7"/>
+      <c r="A78" s="7"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="N78" s="8"/>
+      <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="8"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="7"/>
-      <c r="R79" s="7"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+      <c r="N79" s="8"/>
+      <c r="O79" s="8"/>
+      <c r="P79" s="8"/>
+      <c r="Q79" s="8"/>
+      <c r="R79" s="8"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="7"/>
+      <c r="A80" s="7"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+      <c r="N80" s="8"/>
+      <c r="O80" s="8"/>
+      <c r="P80" s="8"/>
+      <c r="Q80" s="8"/>
+      <c r="R80" s="8"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="7"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+      <c r="N81" s="8"/>
+      <c r="O81" s="8"/>
+      <c r="P81" s="8"/>
+      <c r="Q81" s="8"/>
+      <c r="R81" s="8"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
-      <c r="P82" s="7"/>
-      <c r="Q82" s="7"/>
-      <c r="R82" s="7"/>
+      <c r="A82" s="7"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
+      <c r="N82" s="8"/>
+      <c r="O82" s="8"/>
+      <c r="P82" s="8"/>
+      <c r="Q82" s="8"/>
+      <c r="R82" s="8"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
-      <c r="N83" s="7"/>
-      <c r="O83" s="7"/>
-      <c r="P83" s="7"/>
-      <c r="Q83" s="7"/>
-      <c r="R83" s="7"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+      <c r="N83" s="8"/>
+      <c r="O83" s="8"/>
+      <c r="P83" s="8"/>
+      <c r="Q83" s="8"/>
+      <c r="R83" s="8"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="7"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
-      <c r="O84" s="7"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="7"/>
-      <c r="R84" s="7"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+      <c r="N84" s="8"/>
+      <c r="O84" s="8"/>
+      <c r="P84" s="8"/>
+      <c r="Q84" s="8"/>
+      <c r="R84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
-      <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="7"/>
-      <c r="R85" s="7"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+      <c r="N85" s="8"/>
+      <c r="O85" s="8"/>
+      <c r="P85" s="8"/>
+      <c r="Q85" s="8"/>
+      <c r="R85" s="8"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
-      <c r="N86" s="7"/>
-      <c r="O86" s="7"/>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="7"/>
-      <c r="R86" s="7"/>
+      <c r="A86" s="7"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8"/>
+      <c r="O86" s="8"/>
+      <c r="P86" s="8"/>
+      <c r="Q86" s="8"/>
+      <c r="R86" s="8"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="7"/>
-      <c r="K87" s="7"/>
-      <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
-      <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="7"/>
-      <c r="R87" s="7"/>
+      <c r="A87" s="7"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+      <c r="N87" s="8"/>
+      <c r="O87" s="8"/>
+      <c r="P87" s="8"/>
+      <c r="Q87" s="8"/>
+      <c r="R87" s="8"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="8"/>
-      <c r="J88" s="7"/>
-      <c r="K88" s="7"/>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
-      <c r="N88" s="7"/>
-      <c r="O88" s="7"/>
-      <c r="P88" s="7"/>
-      <c r="Q88" s="7"/>
-      <c r="R88" s="7"/>
+      <c r="A88" s="7"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="N88" s="8"/>
+      <c r="O88" s="8"/>
+      <c r="P88" s="8"/>
+      <c r="Q88" s="8"/>
+      <c r="R88" s="8"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="7"/>
-      <c r="R89" s="7"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
+      <c r="N89" s="8"/>
+      <c r="O89" s="8"/>
+      <c r="P89" s="8"/>
+      <c r="Q89" s="8"/>
+      <c r="R89" s="8"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="7"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
-      <c r="N90" s="7"/>
-      <c r="O90" s="7"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="7"/>
-      <c r="R90" s="7"/>
+      <c r="A90" s="7"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
+      <c r="N90" s="8"/>
+      <c r="O90" s="8"/>
+      <c r="P90" s="8"/>
+      <c r="Q90" s="8"/>
+      <c r="R90" s="8"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="7"/>
-      <c r="K91" s="7"/>
-      <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
-      <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="7"/>
+      <c r="A91" s="7"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
+      <c r="N91" s="8"/>
+      <c r="O91" s="8"/>
+      <c r="P91" s="8"/>
+      <c r="Q91" s="8"/>
+      <c r="R91" s="8"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="7"/>
+      <c r="A92" s="7"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="8"/>
+      <c r="N92" s="8"/>
+      <c r="O92" s="8"/>
+      <c r="P92" s="8"/>
+      <c r="Q92" s="8"/>
+      <c r="R92" s="8"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="7"/>
-      <c r="K93" s="7"/>
-      <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
-      <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="7"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
+      <c r="N93" s="8"/>
+      <c r="O93" s="8"/>
+      <c r="P93" s="8"/>
+      <c r="Q93" s="8"/>
+      <c r="R93" s="8"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="8"/>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="7"/>
-      <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
-      <c r="O94" s="7"/>
-      <c r="P94" s="7"/>
-      <c r="Q94" s="7"/>
-      <c r="R94" s="7"/>
+      <c r="A94" s="7"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
+      <c r="N94" s="8"/>
+      <c r="O94" s="8"/>
+      <c r="P94" s="8"/>
+      <c r="Q94" s="8"/>
+      <c r="R94" s="8"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
-      <c r="N95" s="7"/>
-      <c r="O95" s="7"/>
-      <c r="P95" s="7"/>
-      <c r="Q95" s="7"/>
-      <c r="R95" s="7"/>
+      <c r="A95" s="7"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
+      <c r="N95" s="8"/>
+      <c r="O95" s="8"/>
+      <c r="P95" s="8"/>
+      <c r="Q95" s="8"/>
+      <c r="R95" s="8"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="7"/>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
-      <c r="O96" s="7"/>
-      <c r="P96" s="7"/>
-      <c r="Q96" s="7"/>
-      <c r="R96" s="7"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
+      <c r="N96" s="8"/>
+      <c r="O96" s="8"/>
+      <c r="P96" s="8"/>
+      <c r="Q96" s="8"/>
+      <c r="R96" s="8"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7"/>
-      <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
-      <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
-      <c r="P97" s="7"/>
-      <c r="Q97" s="7"/>
-      <c r="R97" s="7"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="8"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8"/>
+      <c r="Q97" s="8"/>
+      <c r="R97" s="8"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="7"/>
-      <c r="K98" s="7"/>
-      <c r="L98" s="7"/>
-      <c r="M98" s="7"/>
-      <c r="N98" s="7"/>
-      <c r="O98" s="7"/>
-      <c r="P98" s="7"/>
-      <c r="Q98" s="7"/>
-      <c r="R98" s="7"/>
+      <c r="A98" s="7"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
+      <c r="N98" s="8"/>
+      <c r="O98" s="8"/>
+      <c r="P98" s="8"/>
+      <c r="Q98" s="8"/>
+      <c r="R98" s="8"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="8"/>
-      <c r="J99" s="7"/>
-      <c r="K99" s="7"/>
-      <c r="L99" s="7"/>
-      <c r="M99" s="7"/>
-      <c r="N99" s="7"/>
-      <c r="O99" s="7"/>
-      <c r="P99" s="7"/>
-      <c r="Q99" s="7"/>
-      <c r="R99" s="7"/>
+      <c r="A99" s="7"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="8"/>
+      <c r="O99" s="8"/>
+      <c r="P99" s="8"/>
+      <c r="Q99" s="8"/>
+      <c r="R99" s="8"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="7"/>
-      <c r="K100" s="7"/>
-      <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
-      <c r="N100" s="7"/>
-      <c r="O100" s="7"/>
-      <c r="P100" s="7"/>
-      <c r="Q100" s="7"/>
-      <c r="R100" s="7"/>
+      <c r="A100" s="7"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
+      <c r="O100" s="8"/>
+      <c r="P100" s="8"/>
+      <c r="Q100" s="8"/>
+      <c r="R100" s="8"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="8"/>
-      <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
-      <c r="N101" s="7"/>
-      <c r="O101" s="7"/>
-      <c r="P101" s="7"/>
-      <c r="Q101" s="7"/>
-      <c r="R101" s="7"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="N101" s="8"/>
+      <c r="O101" s="8"/>
+      <c r="P101" s="8"/>
+      <c r="Q101" s="8"/>
+      <c r="R101" s="8"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="8"/>
-      <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
-      <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
-      <c r="N102" s="7"/>
-      <c r="O102" s="7"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="7"/>
-      <c r="R102" s="7"/>
+      <c r="A102" s="7"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="8"/>
+      <c r="O102" s="8"/>
+      <c r="P102" s="8"/>
+      <c r="Q102" s="8"/>
+      <c r="R102" s="8"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6"/>
-      <c r="B103" s="7"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="8"/>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
-      <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
-      <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
-      <c r="P103" s="7"/>
-      <c r="Q103" s="7"/>
-      <c r="R103" s="7"/>
+      <c r="A103" s="7"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
+      <c r="N103" s="8"/>
+      <c r="O103" s="8"/>
+      <c r="P103" s="8"/>
+      <c r="Q103" s="8"/>
+      <c r="R103" s="8"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7"/>
-      <c r="I104" s="8"/>
-      <c r="J104" s="7"/>
-      <c r="K104" s="7"/>
-      <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
-      <c r="N104" s="7"/>
-      <c r="O104" s="7"/>
-      <c r="P104" s="7"/>
-      <c r="Q104" s="7"/>
-      <c r="R104" s="7"/>
+      <c r="A104" s="7"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+      <c r="M104" s="8"/>
+      <c r="N104" s="8"/>
+      <c r="O104" s="8"/>
+      <c r="P104" s="8"/>
+      <c r="Q104" s="8"/>
+      <c r="R104" s="8"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="7"/>
-      <c r="K105" s="7"/>
-      <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
-      <c r="N105" s="7"/>
-      <c r="O105" s="7"/>
-      <c r="P105" s="7"/>
-      <c r="Q105" s="7"/>
-      <c r="R105" s="7"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
+      <c r="P105" s="8"/>
+      <c r="Q105" s="8"/>
+      <c r="R105" s="8"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="7"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7"/>
-      <c r="N106" s="7"/>
-      <c r="O106" s="7"/>
-      <c r="P106" s="7"/>
-      <c r="Q106" s="7"/>
-      <c r="R106" s="7"/>
+      <c r="A106" s="7"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="N106" s="8"/>
+      <c r="O106" s="8"/>
+      <c r="P106" s="8"/>
+      <c r="Q106" s="8"/>
+      <c r="R106" s="8"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="8"/>
-      <c r="J107" s="7"/>
-      <c r="K107" s="7"/>
-      <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
-      <c r="N107" s="7"/>
-      <c r="O107" s="7"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="7"/>
-      <c r="R107" s="7"/>
+      <c r="A107" s="7"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="M107" s="8"/>
+      <c r="N107" s="8"/>
+      <c r="O107" s="8"/>
+      <c r="P107" s="8"/>
+      <c r="Q107" s="8"/>
+      <c r="R107" s="8"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="8"/>
-      <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
-      <c r="P108" s="7"/>
-      <c r="Q108" s="7"/>
-      <c r="R108" s="7"/>
+      <c r="A108" s="7"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+      <c r="M108" s="8"/>
+      <c r="N108" s="8"/>
+      <c r="O108" s="8"/>
+      <c r="P108" s="8"/>
+      <c r="Q108" s="8"/>
+      <c r="R108" s="8"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="8"/>
-      <c r="J109" s="7"/>
-      <c r="K109" s="7"/>
-      <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="7"/>
-      <c r="R109" s="7"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+      <c r="M109" s="8"/>
+      <c r="N109" s="8"/>
+      <c r="O109" s="8"/>
+      <c r="P109" s="8"/>
+      <c r="Q109" s="8"/>
+      <c r="R109" s="8"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="8"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="7"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="7"/>
+      <c r="A110" s="7"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+      <c r="M110" s="8"/>
+      <c r="N110" s="8"/>
+      <c r="O110" s="8"/>
+      <c r="P110" s="8"/>
+      <c r="Q110" s="8"/>
+      <c r="R110" s="8"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="8"/>
-      <c r="J111" s="7"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="7"/>
-      <c r="Q111" s="7"/>
-      <c r="R111" s="7"/>
+      <c r="A111" s="7"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+      <c r="M111" s="8"/>
+      <c r="N111" s="8"/>
+      <c r="O111" s="8"/>
+      <c r="P111" s="8"/>
+      <c r="Q111" s="8"/>
+      <c r="R111" s="8"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="8"/>
-      <c r="J112" s="7"/>
-      <c r="K112" s="7"/>
-      <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
-      <c r="N112" s="7"/>
-      <c r="O112" s="7"/>
-      <c r="P112" s="7"/>
-      <c r="Q112" s="7"/>
-      <c r="R112" s="7"/>
+      <c r="A112" s="7"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+      <c r="M112" s="8"/>
+      <c r="N112" s="8"/>
+      <c r="O112" s="8"/>
+      <c r="P112" s="8"/>
+      <c r="Q112" s="8"/>
+      <c r="R112" s="8"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="8"/>
-      <c r="J113" s="7"/>
-      <c r="K113" s="7"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
-      <c r="N113" s="7"/>
-      <c r="O113" s="7"/>
-      <c r="P113" s="7"/>
-      <c r="Q113" s="7"/>
-      <c r="R113" s="7"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+      <c r="M113" s="8"/>
+      <c r="N113" s="8"/>
+      <c r="O113" s="8"/>
+      <c r="P113" s="8"/>
+      <c r="Q113" s="8"/>
+      <c r="R113" s="8"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="6"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="7"/>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
-      <c r="N114" s="7"/>
-      <c r="O114" s="7"/>
-      <c r="P114" s="7"/>
-      <c r="Q114" s="7"/>
-      <c r="R114" s="7"/>
+      <c r="A114" s="7"/>
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="8"/>
+      <c r="L114" s="8"/>
+      <c r="M114" s="8"/>
+      <c r="N114" s="8"/>
+      <c r="O114" s="8"/>
+      <c r="P114" s="8"/>
+      <c r="Q114" s="8"/>
+      <c r="R114" s="8"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="7"/>
-      <c r="K115" s="7"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
-      <c r="N115" s="7"/>
-      <c r="O115" s="7"/>
-      <c r="P115" s="7"/>
-      <c r="Q115" s="7"/>
-      <c r="R115" s="7"/>
+      <c r="A115" s="7"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="9"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
+      <c r="N115" s="8"/>
+      <c r="O115" s="8"/>
+      <c r="P115" s="8"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="8"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="6"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="8"/>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
-      <c r="O116" s="7"/>
-      <c r="P116" s="7"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="7"/>
+      <c r="A116" s="7"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+      <c r="M116" s="8"/>
+      <c r="N116" s="8"/>
+      <c r="O116" s="8"/>
+      <c r="P116" s="8"/>
+      <c r="Q116" s="8"/>
+      <c r="R116" s="8"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="8"/>
-      <c r="J117" s="7"/>
-      <c r="K117" s="7"/>
-      <c r="L117" s="7"/>
-      <c r="M117" s="7"/>
-      <c r="N117" s="7"/>
-      <c r="O117" s="7"/>
-      <c r="P117" s="7"/>
-      <c r="Q117" s="7"/>
-      <c r="R117" s="7"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+      <c r="M117" s="8"/>
+      <c r="N117" s="8"/>
+      <c r="O117" s="8"/>
+      <c r="P117" s="8"/>
+      <c r="Q117" s="8"/>
+      <c r="R117" s="8"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="8"/>
-      <c r="J118" s="7"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
-      <c r="O118" s="7"/>
-      <c r="P118" s="7"/>
-      <c r="Q118" s="7"/>
-      <c r="R118" s="7"/>
+      <c r="A118" s="7"/>
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="8"/>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
+      <c r="N118" s="8"/>
+      <c r="O118" s="8"/>
+      <c r="P118" s="8"/>
+      <c r="Q118" s="8"/>
+      <c r="R118" s="8"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="7"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="7"/>
-      <c r="Q119" s="7"/>
-      <c r="R119" s="7"/>
+      <c r="A119" s="7"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+      <c r="I119" s="9"/>
+      <c r="J119" s="8"/>
+      <c r="K119" s="8"/>
+      <c r="L119" s="8"/>
+      <c r="M119" s="8"/>
+      <c r="N119" s="8"/>
+      <c r="O119" s="8"/>
+      <c r="P119" s="8"/>
+      <c r="Q119" s="8"/>
+      <c r="R119" s="8"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="6"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="8"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="7"/>
+      <c r="A120" s="7"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="8"/>
+      <c r="L120" s="8"/>
+      <c r="M120" s="8"/>
+      <c r="N120" s="8"/>
+      <c r="O120" s="8"/>
+      <c r="P120" s="8"/>
+      <c r="Q120" s="8"/>
+      <c r="R120" s="8"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="6"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="8"/>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="7"/>
-      <c r="P121" s="7"/>
-      <c r="Q121" s="7"/>
-      <c r="R121" s="7"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="9"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
+      <c r="N121" s="8"/>
+      <c r="O121" s="8"/>
+      <c r="P121" s="8"/>
+      <c r="Q121" s="8"/>
+      <c r="R121" s="8"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="6"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
-      <c r="O122" s="7"/>
-      <c r="P122" s="7"/>
-      <c r="Q122" s="7"/>
-      <c r="R122" s="7"/>
+      <c r="A122" s="7"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="9"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="8"/>
+      <c r="L122" s="8"/>
+      <c r="M122" s="8"/>
+      <c r="N122" s="8"/>
+      <c r="O122" s="8"/>
+      <c r="P122" s="8"/>
+      <c r="Q122" s="8"/>
+      <c r="R122" s="8"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="6"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
-      <c r="N123" s="7"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="7"/>
-      <c r="Q123" s="7"/>
-      <c r="R123" s="7"/>
+      <c r="A123" s="7"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="8"/>
+      <c r="G123" s="8"/>
+      <c r="H123" s="8"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="8"/>
+      <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
+      <c r="N123" s="8"/>
+      <c r="O123" s="8"/>
+      <c r="P123" s="8"/>
+      <c r="Q123" s="8"/>
+      <c r="R123" s="8"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="6"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="8"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
+      <c r="A124" s="7"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="8"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="8"/>
+      <c r="L124" s="8"/>
+      <c r="M124" s="8"/>
+      <c r="N124" s="8"/>
+      <c r="O124" s="8"/>
+      <c r="P124" s="8"/>
+      <c r="Q124" s="8"/>
+      <c r="R124" s="8"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="8"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="7"/>
+      <c r="A125" s="7"/>
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="8"/>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
+      <c r="N125" s="8"/>
+      <c r="O125" s="8"/>
+      <c r="P125" s="8"/>
+      <c r="Q125" s="8"/>
+      <c r="R125" s="8"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="6"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="8"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="7"/>
+      <c r="A126" s="7"/>
+      <c r="B126" s="8"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="8"/>
+      <c r="G126" s="8"/>
+      <c r="H126" s="8"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="8"/>
+      <c r="L126" s="8"/>
+      <c r="M126" s="8"/>
+      <c r="N126" s="8"/>
+      <c r="O126" s="8"/>
+      <c r="P126" s="8"/>
+      <c r="Q126" s="8"/>
+      <c r="R126" s="8"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="6"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="7"/>
+      <c r="A127" s="7"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="8"/>
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="8"/>
+      <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
+      <c r="N127" s="8"/>
+      <c r="O127" s="8"/>
+      <c r="P127" s="8"/>
+      <c r="Q127" s="8"/>
+      <c r="R127" s="8"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="6"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="8"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="7"/>
+      <c r="A128" s="7"/>
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="8"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="8"/>
+      <c r="L128" s="8"/>
+      <c r="M128" s="8"/>
+      <c r="N128" s="8"/>
+      <c r="O128" s="8"/>
+      <c r="P128" s="8"/>
+      <c r="Q128" s="8"/>
+      <c r="R128" s="8"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="6"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-      <c r="H129" s="7"/>
-      <c r="I129" s="8"/>
-      <c r="J129" s="7"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="7"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="7"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="7"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="8"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="8"/>
+      <c r="E129" s="8"/>
+      <c r="F129" s="8"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="8"/>
+      <c r="L129" s="8"/>
+      <c r="M129" s="8"/>
+      <c r="N129" s="8"/>
+      <c r="O129" s="8"/>
+      <c r="P129" s="8"/>
+      <c r="Q129" s="8"/>
+      <c r="R129" s="8"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="6"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="8"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="7"/>
+      <c r="A130" s="7"/>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="8"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
+      <c r="N130" s="8"/>
+      <c r="O130" s="8"/>
+      <c r="P130" s="8"/>
+      <c r="Q130" s="8"/>
+      <c r="R130" s="8"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="6"/>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="7"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7"/>
-      <c r="M131" s="7"/>
-      <c r="N131" s="7"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="7"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="7"/>
+      <c r="A131" s="7"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="8"/>
+      <c r="M131" s="8"/>
+      <c r="N131" s="8"/>
+      <c r="O131" s="8"/>
+      <c r="P131" s="8"/>
+      <c r="Q131" s="8"/>
+      <c r="R131" s="8"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="6"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="8"/>
-      <c r="J132" s="7"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
-      <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="7"/>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="7"/>
+      <c r="A132" s="7"/>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="8"/>
+      <c r="K132" s="8"/>
+      <c r="L132" s="8"/>
+      <c r="M132" s="8"/>
+      <c r="N132" s="8"/>
+      <c r="O132" s="8"/>
+      <c r="P132" s="8"/>
+      <c r="Q132" s="8"/>
+      <c r="R132" s="8"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="6"/>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="8"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
-      <c r="N133" s="7"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="7"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="8"/>
+      <c r="F133" s="8"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="8"/>
+      <c r="K133" s="8"/>
+      <c r="L133" s="8"/>
+      <c r="M133" s="8"/>
+      <c r="N133" s="8"/>
+      <c r="O133" s="8"/>
+      <c r="P133" s="8"/>
+      <c r="Q133" s="8"/>
+      <c r="R133" s="8"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="6"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="8"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="7"/>
+      <c r="A134" s="7"/>
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="8"/>
+      <c r="E134" s="8"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="8"/>
+      <c r="K134" s="8"/>
+      <c r="L134" s="8"/>
+      <c r="M134" s="8"/>
+      <c r="N134" s="8"/>
+      <c r="O134" s="8"/>
+      <c r="P134" s="8"/>
+      <c r="Q134" s="8"/>
+      <c r="R134" s="8"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="6"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="7"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="7"/>
-      <c r="N135" s="7"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="7"/>
-      <c r="Q135" s="7"/>
-      <c r="R135" s="7"/>
+      <c r="A135" s="7"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="8"/>
+      <c r="E135" s="8"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="8"/>
+      <c r="K135" s="8"/>
+      <c r="L135" s="8"/>
+      <c r="M135" s="8"/>
+      <c r="N135" s="8"/>
+      <c r="O135" s="8"/>
+      <c r="P135" s="8"/>
+      <c r="Q135" s="8"/>
+      <c r="R135" s="8"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="6"/>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="8"/>
-      <c r="J136" s="7"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="7"/>
+      <c r="A136" s="7"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
+      <c r="E136" s="8"/>
+      <c r="F136" s="8"/>
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+      <c r="I136" s="9"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="8"/>
+      <c r="L136" s="8"/>
+      <c r="M136" s="8"/>
+      <c r="N136" s="8"/>
+      <c r="O136" s="8"/>
+      <c r="P136" s="8"/>
+      <c r="Q136" s="8"/>
+      <c r="R136" s="8"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="8"/>
-      <c r="J137" s="7"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="7"/>
+      <c r="A137" s="7"/>
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="8"/>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="9"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="8"/>
+      <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
+      <c r="N137" s="8"/>
+      <c r="O137" s="8"/>
+      <c r="P137" s="8"/>
+      <c r="Q137" s="8"/>
+      <c r="R137" s="8"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="6"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="8"/>
-      <c r="J138" s="7"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="7"/>
-      <c r="N138" s="7"/>
-      <c r="O138" s="7"/>
-      <c r="P138" s="7"/>
-      <c r="Q138" s="7"/>
-      <c r="R138" s="7"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+      <c r="I138" s="9"/>
+      <c r="J138" s="8"/>
+      <c r="K138" s="8"/>
+      <c r="L138" s="8"/>
+      <c r="M138" s="8"/>
+      <c r="N138" s="8"/>
+      <c r="O138" s="8"/>
+      <c r="P138" s="8"/>
+      <c r="Q138" s="8"/>
+      <c r="R138" s="8"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="6"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
-      <c r="I139" s="8"/>
-      <c r="J139" s="7"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="7"/>
-      <c r="R139" s="7"/>
+      <c r="A139" s="7"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="8"/>
+      <c r="E139" s="8"/>
+      <c r="F139" s="8"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="8"/>
+      <c r="L139" s="8"/>
+      <c r="M139" s="8"/>
+      <c r="N139" s="8"/>
+      <c r="O139" s="8"/>
+      <c r="P139" s="8"/>
+      <c r="Q139" s="8"/>
+      <c r="R139" s="8"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="6"/>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-      <c r="I140" s="8"/>
-      <c r="J140" s="7"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="7"/>
-      <c r="N140" s="7"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="7"/>
-      <c r="Q140" s="7"/>
-      <c r="R140" s="7"/>
+      <c r="A140" s="7"/>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8"/>
+      <c r="I140" s="9"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="8"/>
+      <c r="L140" s="8"/>
+      <c r="M140" s="8"/>
+      <c r="N140" s="8"/>
+      <c r="O140" s="8"/>
+      <c r="P140" s="8"/>
+      <c r="Q140" s="8"/>
+      <c r="R140" s="8"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="6"/>
-      <c r="B141" s="7"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="7"/>
-      <c r="I141" s="8"/>
-      <c r="J141" s="7"/>
-      <c r="K141" s="7"/>
-      <c r="L141" s="7"/>
-      <c r="M141" s="7"/>
-      <c r="N141" s="7"/>
-      <c r="O141" s="7"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="7"/>
-      <c r="R141" s="7"/>
+      <c r="A141" s="7"/>
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="8"/>
+      <c r="E141" s="8"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="8"/>
+      <c r="L141" s="8"/>
+      <c r="M141" s="8"/>
+      <c r="N141" s="8"/>
+      <c r="O141" s="8"/>
+      <c r="P141" s="8"/>
+      <c r="Q141" s="8"/>
+      <c r="R141" s="8"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="6"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
-      <c r="I142" s="8"/>
-      <c r="J142" s="7"/>
-      <c r="K142" s="7"/>
-      <c r="L142" s="7"/>
-      <c r="M142" s="7"/>
-      <c r="N142" s="7"/>
-      <c r="O142" s="7"/>
-      <c r="P142" s="7"/>
-      <c r="Q142" s="7"/>
-      <c r="R142" s="7"/>
+      <c r="A142" s="7"/>
+      <c r="B142" s="8"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="8"/>
+      <c r="L142" s="8"/>
+      <c r="M142" s="8"/>
+      <c r="N142" s="8"/>
+      <c r="O142" s="8"/>
+      <c r="P142" s="8"/>
+      <c r="Q142" s="8"/>
+      <c r="R142" s="8"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="6"/>
-      <c r="B143" s="7"/>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
-      <c r="I143" s="8"/>
-      <c r="J143" s="7"/>
-      <c r="K143" s="7"/>
-      <c r="L143" s="7"/>
-      <c r="M143" s="7"/>
-      <c r="N143" s="7"/>
-      <c r="O143" s="7"/>
-      <c r="P143" s="7"/>
-      <c r="Q143" s="7"/>
-      <c r="R143" s="7"/>
+      <c r="A143" s="7"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="8"/>
+      <c r="K143" s="8"/>
+      <c r="L143" s="8"/>
+      <c r="M143" s="8"/>
+      <c r="N143" s="8"/>
+      <c r="O143" s="8"/>
+      <c r="P143" s="8"/>
+      <c r="Q143" s="8"/>
+      <c r="R143" s="8"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="6"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
-      <c r="I144" s="8"/>
-      <c r="J144" s="7"/>
-      <c r="K144" s="7"/>
-      <c r="L144" s="7"/>
-      <c r="M144" s="7"/>
-      <c r="N144" s="7"/>
-      <c r="O144" s="7"/>
-      <c r="P144" s="7"/>
-      <c r="Q144" s="7"/>
-      <c r="R144" s="7"/>
+      <c r="A144" s="7"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="9"/>
+      <c r="J144" s="8"/>
+      <c r="K144" s="8"/>
+      <c r="L144" s="8"/>
+      <c r="M144" s="8"/>
+      <c r="N144" s="8"/>
+      <c r="O144" s="8"/>
+      <c r="P144" s="8"/>
+      <c r="Q144" s="8"/>
+      <c r="R144" s="8"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="6"/>
-      <c r="B145" s="7"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
-      <c r="I145" s="8"/>
-      <c r="J145" s="7"/>
-      <c r="K145" s="7"/>
-      <c r="L145" s="7"/>
-      <c r="M145" s="7"/>
-      <c r="N145" s="7"/>
-      <c r="O145" s="7"/>
-      <c r="P145" s="7"/>
-      <c r="Q145" s="7"/>
-      <c r="R145" s="7"/>
+      <c r="A145" s="7"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="8"/>
+      <c r="K145" s="8"/>
+      <c r="L145" s="8"/>
+      <c r="M145" s="8"/>
+      <c r="N145" s="8"/>
+      <c r="O145" s="8"/>
+      <c r="P145" s="8"/>
+      <c r="Q145" s="8"/>
+      <c r="R145" s="8"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="6"/>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-      <c r="I146" s="8"/>
-      <c r="J146" s="7"/>
-      <c r="K146" s="7"/>
-      <c r="L146" s="7"/>
-      <c r="M146" s="7"/>
-      <c r="N146" s="7"/>
-      <c r="O146" s="7"/>
-      <c r="P146" s="7"/>
-      <c r="Q146" s="7"/>
-      <c r="R146" s="7"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="9"/>
+      <c r="J146" s="8"/>
+      <c r="K146" s="8"/>
+      <c r="L146" s="8"/>
+      <c r="M146" s="8"/>
+      <c r="N146" s="8"/>
+      <c r="O146" s="8"/>
+      <c r="P146" s="8"/>
+      <c r="Q146" s="8"/>
+      <c r="R146" s="8"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="6"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="8"/>
-      <c r="J147" s="7"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="7"/>
-      <c r="Q147" s="7"/>
-      <c r="R147" s="7"/>
+      <c r="A147" s="7"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="9"/>
+      <c r="J147" s="8"/>
+      <c r="K147" s="8"/>
+      <c r="L147" s="8"/>
+      <c r="M147" s="8"/>
+      <c r="N147" s="8"/>
+      <c r="O147" s="8"/>
+      <c r="P147" s="8"/>
+      <c r="Q147" s="8"/>
+      <c r="R147" s="8"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="6"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
-      <c r="I148" s="8"/>
-      <c r="J148" s="7"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
-      <c r="N148" s="7"/>
-      <c r="O148" s="7"/>
-      <c r="P148" s="7"/>
-      <c r="Q148" s="7"/>
-      <c r="R148" s="7"/>
+      <c r="A148" s="7"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="9"/>
+      <c r="J148" s="8"/>
+      <c r="K148" s="8"/>
+      <c r="L148" s="8"/>
+      <c r="M148" s="8"/>
+      <c r="N148" s="8"/>
+      <c r="O148" s="8"/>
+      <c r="P148" s="8"/>
+      <c r="Q148" s="8"/>
+      <c r="R148" s="8"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="6"/>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-      <c r="I149" s="8"/>
-      <c r="J149" s="7"/>
-      <c r="K149" s="7"/>
-      <c r="L149" s="7"/>
-      <c r="M149" s="7"/>
-      <c r="N149" s="7"/>
-      <c r="O149" s="7"/>
-      <c r="P149" s="7"/>
-      <c r="Q149" s="7"/>
-      <c r="R149" s="7"/>
+      <c r="A149" s="7"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+      <c r="I149" s="9"/>
+      <c r="J149" s="8"/>
+      <c r="K149" s="8"/>
+      <c r="L149" s="8"/>
+      <c r="M149" s="8"/>
+      <c r="N149" s="8"/>
+      <c r="O149" s="8"/>
+      <c r="P149" s="8"/>
+      <c r="Q149" s="8"/>
+      <c r="R149" s="8"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="6"/>
-      <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
-      <c r="I150" s="8"/>
-      <c r="J150" s="7"/>
-      <c r="K150" s="7"/>
-      <c r="L150" s="7"/>
-      <c r="M150" s="7"/>
-      <c r="N150" s="7"/>
-      <c r="O150" s="7"/>
-      <c r="P150" s="7"/>
-      <c r="Q150" s="7"/>
-      <c r="R150" s="7"/>
+      <c r="A150" s="7"/>
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="8"/>
+      <c r="F150" s="8"/>
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="9"/>
+      <c r="J150" s="8"/>
+      <c r="K150" s="8"/>
+      <c r="L150" s="8"/>
+      <c r="M150" s="8"/>
+      <c r="N150" s="8"/>
+      <c r="O150" s="8"/>
+      <c r="P150" s="8"/>
+      <c r="Q150" s="8"/>
+      <c r="R150" s="8"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="6"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="7"/>
-      <c r="I151" s="8"/>
-      <c r="J151" s="7"/>
-      <c r="K151" s="7"/>
-      <c r="L151" s="7"/>
-      <c r="M151" s="7"/>
-      <c r="N151" s="7"/>
-      <c r="O151" s="7"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="7"/>
-      <c r="R151" s="7"/>
+      <c r="A151" s="7"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="8"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="8"/>
+      <c r="K151" s="8"/>
+      <c r="L151" s="8"/>
+      <c r="M151" s="8"/>
+      <c r="N151" s="8"/>
+      <c r="O151" s="8"/>
+      <c r="P151" s="8"/>
+      <c r="Q151" s="8"/>
+      <c r="R151" s="8"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="6"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-      <c r="I152" s="8"/>
-      <c r="J152" s="7"/>
-      <c r="K152" s="7"/>
-      <c r="L152" s="7"/>
-      <c r="M152" s="7"/>
-      <c r="N152" s="7"/>
-      <c r="O152" s="7"/>
-      <c r="P152" s="7"/>
-      <c r="Q152" s="7"/>
-      <c r="R152" s="7"/>
+      <c r="A152" s="7"/>
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="8"/>
+      <c r="G152" s="8"/>
+      <c r="H152" s="8"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="8"/>
+      <c r="K152" s="8"/>
+      <c r="L152" s="8"/>
+      <c r="M152" s="8"/>
+      <c r="N152" s="8"/>
+      <c r="O152" s="8"/>
+      <c r="P152" s="8"/>
+      <c r="Q152" s="8"/>
+      <c r="R152" s="8"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="6"/>
-      <c r="B153" s="7"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-      <c r="I153" s="8"/>
-      <c r="J153" s="7"/>
-      <c r="K153" s="7"/>
-      <c r="L153" s="7"/>
-      <c r="M153" s="7"/>
-      <c r="N153" s="7"/>
-      <c r="O153" s="7"/>
-      <c r="P153" s="7"/>
-      <c r="Q153" s="7"/>
-      <c r="R153" s="7"/>
+      <c r="A153" s="7"/>
+      <c r="B153" s="8"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="8"/>
+      <c r="E153" s="8"/>
+      <c r="F153" s="8"/>
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
+      <c r="I153" s="9"/>
+      <c r="J153" s="8"/>
+      <c r="K153" s="8"/>
+      <c r="L153" s="8"/>
+      <c r="M153" s="8"/>
+      <c r="N153" s="8"/>
+      <c r="O153" s="8"/>
+      <c r="P153" s="8"/>
+      <c r="Q153" s="8"/>
+      <c r="R153" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5146,7 +5150,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K4" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q4" type="list">
@@ -5154,7 +5158,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R4" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B5" type="list">
@@ -5170,7 +5174,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5" type="list">
@@ -5178,7 +5182,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R5" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B6" type="list">
@@ -5194,7 +5198,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K6" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q6" type="list">
@@ -5202,7 +5206,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R6" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B7" type="list">
@@ -5218,7 +5222,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K7" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q7" type="list">
@@ -5226,7 +5230,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R7" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B8" type="list">
@@ -5242,7 +5246,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K8" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q8" type="list">
@@ -5250,7 +5254,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R8" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B9" type="list">
@@ -5266,7 +5270,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K9" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q9" type="list">
@@ -5274,7 +5278,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R9" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B10" type="list">
@@ -5290,7 +5294,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K10" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q10" type="list">
@@ -5298,7 +5302,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R10" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B11" type="list">
@@ -5314,7 +5318,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K11" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q11" type="list">
@@ -5322,7 +5326,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R11" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B12" type="list">
@@ -5338,7 +5342,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K12" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q12" type="list">
@@ -5346,7 +5350,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R12" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B13" type="list">
@@ -5362,7 +5366,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K13" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q13" type="list">
@@ -5370,7 +5374,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R13" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B14" type="list">
@@ -5386,7 +5390,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K14" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q14" type="list">
@@ -5394,7 +5398,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R14" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B15" type="list">
@@ -5410,7 +5414,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K15" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q15" type="list">
@@ -5418,7 +5422,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R15" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B16" type="list">
@@ -5434,7 +5438,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K16" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q16" type="list">
@@ -5442,7 +5446,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R16" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B17" type="list">
@@ -5458,7 +5462,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K17" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q17" type="list">
@@ -5466,7 +5470,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R17" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B18" type="list">
@@ -5482,7 +5486,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K18" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q18" type="list">
@@ -5490,7 +5494,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R18" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B19" type="list">
@@ -5506,7 +5510,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K19" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q19" type="list">
@@ -5514,7 +5518,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R19" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B20" type="list">
@@ -5530,7 +5534,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K20" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q20" type="list">
@@ -5538,7 +5542,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R20" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B21" type="list">
@@ -5554,7 +5558,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K21" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q21" type="list">
@@ -5562,7 +5566,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R21" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B22" type="list">
@@ -5578,7 +5582,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K22" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q22" type="list">
@@ -5586,7 +5590,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R22" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B23" type="list">
@@ -5602,7 +5606,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K23" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q23" type="list">
@@ -5610,7 +5614,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R23" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C24" type="list">
@@ -5630,7 +5634,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q24" type="list">
@@ -5638,7 +5642,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R24" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C25" type="list">
@@ -5658,7 +5662,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K25" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q25" type="list">
@@ -5666,7 +5670,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R25" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C26" type="list">
@@ -5686,7 +5690,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K26" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q26" type="list">
@@ -5694,7 +5698,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R26" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C27" type="list">
@@ -5714,7 +5718,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K27" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q27" type="list">
@@ -5722,7 +5726,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R27" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C28" type="list">
@@ -5742,7 +5746,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K28" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q28" type="list">
@@ -5750,7 +5754,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R28" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C29" type="list">
@@ -5770,7 +5774,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K29" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q29" type="list">
@@ -5778,7 +5782,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R29" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C30" type="list">
@@ -5798,7 +5802,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K30" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q30" type="list">
@@ -5806,7 +5810,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R30" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C31" type="list">
@@ -5826,7 +5830,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K31" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q31" type="list">
@@ -5834,7 +5838,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R31" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C32" type="list">
@@ -5854,7 +5858,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K32" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q32" type="list">
@@ -5862,7 +5866,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R32" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C33" type="list">
@@ -5882,7 +5886,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K33" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q33" type="list">
@@ -5890,7 +5894,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R33" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C34" type="list">
@@ -5910,7 +5914,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K34" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q34" type="list">
@@ -5918,7 +5922,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R34" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C35" type="list">
@@ -5938,7 +5942,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K35" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q35" type="list">
@@ -5946,7 +5950,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R35" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C36" type="list">
@@ -5966,7 +5970,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K36" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q36" type="list">
@@ -5974,7 +5978,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R36" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C37" type="list">
@@ -5994,7 +5998,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K37" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q37" type="list">
@@ -6002,7 +6006,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R37" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C38" type="list">
@@ -6022,7 +6026,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K38" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q38" type="list">
@@ -6030,7 +6034,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R38" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C39" type="list">
@@ -6050,7 +6054,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K39" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q39" type="list">
@@ -6058,7 +6062,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R39" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C40" type="list">
@@ -6078,7 +6082,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K40" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q40" type="list">
@@ -6086,7 +6090,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R40" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
@@ -6106,7 +6110,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K41" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q41" type="list">
@@ -6114,7 +6118,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R41" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C42" type="list">
@@ -6134,7 +6138,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K42" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q42" type="list">
@@ -6142,7 +6146,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R42" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C43" type="list">
@@ -6162,7 +6166,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q43" type="list">
@@ -6170,7 +6174,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R43" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C44" type="list">
@@ -6190,7 +6194,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K44" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q44" type="list">
@@ -6198,7 +6202,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R44" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C45" type="list">
@@ -6218,7 +6222,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K45" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q45" type="list">
@@ -6226,7 +6230,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R45" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C46" type="list">
@@ -6246,7 +6250,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K46" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q46" type="list">
@@ -6254,7 +6258,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R46" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C47" type="list">
@@ -6274,7 +6278,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K47" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q47" type="list">
@@ -6282,7 +6286,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R47" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C48" type="list">
@@ -6302,7 +6306,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K48" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q48" type="list">
@@ -6310,7 +6314,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R48" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C49" type="list">
@@ -6330,7 +6334,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K49" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q49" type="list">
@@ -6338,7 +6342,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R49" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C50" type="list">
@@ -6358,7 +6362,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K50" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q50" type="list">
@@ -6366,7 +6370,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R50" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C51" type="list">
@@ -6386,7 +6390,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K51" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q51" type="list">
@@ -6394,7 +6398,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R51" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C52" type="list">
@@ -6414,7 +6418,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K52" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q52" type="list">
@@ -6422,7 +6426,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R52" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C53" type="list">
@@ -6442,7 +6446,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K53" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q53" type="list">
@@ -6450,7 +6454,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R53" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C54" type="list">
@@ -6470,7 +6474,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K54" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q54" type="list">
@@ -6478,7 +6482,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R54" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C55" type="list">
@@ -6498,7 +6502,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K55" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q55" type="list">
@@ -6506,7 +6510,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R55" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C56" type="list">
@@ -6526,7 +6530,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K56" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q56" type="list">
@@ -6534,7 +6538,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R56" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C57" type="list">
@@ -6554,7 +6558,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K57" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q57" type="list">
@@ -6562,7 +6566,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R57" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C58" type="list">
@@ -6582,7 +6586,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K58" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q58" type="list">
@@ -6590,7 +6594,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R58" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C59" type="list">
@@ -6610,7 +6614,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K59" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q59" type="list">
@@ -6618,7 +6622,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R59" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
@@ -6638,7 +6642,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K60" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q60" type="list">
@@ -6646,7 +6650,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R60" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C61" type="list">
@@ -6666,7 +6670,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K61" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q61" type="list">
@@ -6674,7 +6678,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R61" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C62" type="list">
@@ -6694,7 +6698,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K62" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q62" type="list">
@@ -6702,7 +6706,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R62" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C63" type="list">
@@ -6722,7 +6726,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K63" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q63" type="list">
@@ -6730,7 +6734,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R63" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C64" type="list">
@@ -6750,7 +6754,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K64" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q64" type="list">
@@ -6758,7 +6762,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R64" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C65" type="list">
@@ -6778,7 +6782,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K65" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q65" type="list">
@@ -6786,7 +6790,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R65" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C66" type="list">
@@ -6806,7 +6810,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K66" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q66" type="list">
@@ -6814,7 +6818,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R66" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C67" type="list">
@@ -6834,7 +6838,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K67" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q67" type="list">
@@ -6842,7 +6846,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R67" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C68" type="list">
@@ -6862,7 +6866,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K68" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q68" type="list">
@@ -6870,7 +6874,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R68" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C69" type="list">
@@ -6890,7 +6894,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K69" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q69" type="list">
@@ -6898,7 +6902,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R69" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C70" type="list">
@@ -6918,7 +6922,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K70" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q70" type="list">
@@ -6926,7 +6930,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R70" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C71" type="list">
@@ -6946,7 +6950,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K71" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q71" type="list">
@@ -6954,7 +6958,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R71" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C72" type="list">
@@ -6974,7 +6978,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K72" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q72" type="list">
@@ -6982,7 +6986,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R72" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C73" type="list">
@@ -7002,7 +7006,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K73" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q73" type="list">
@@ -7010,7 +7014,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R73" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C74" type="list">
@@ -7030,7 +7034,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K74" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q74" type="list">
@@ -7038,7 +7042,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R74" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C75" type="list">
@@ -7058,7 +7062,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K75" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q75" type="list">
@@ -7066,7 +7070,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R75" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C76" type="list">
@@ -7086,7 +7090,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K76" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q76" type="list">
@@ -7094,7 +7098,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R76" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C77" type="list">
@@ -7114,7 +7118,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K77" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q77" type="list">
@@ -7122,7 +7126,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R77" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C78" type="list">
@@ -7142,7 +7146,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K78" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q78" type="list">
@@ -7150,7 +7154,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R78" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C79" type="list">
@@ -7170,7 +7174,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K79" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q79" type="list">
@@ -7178,7 +7182,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R79" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C80" type="list">
@@ -7198,7 +7202,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K80" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q80" type="list">
@@ -7206,7 +7210,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R80" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C81" type="list">
@@ -7226,7 +7230,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K81" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q81" type="list">
@@ -7234,7 +7238,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R81" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C82" type="list">
@@ -7254,7 +7258,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K82" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q82" type="list">
@@ -7262,7 +7266,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R82" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C83" type="list">
@@ -7282,7 +7286,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K83" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q83" type="list">
@@ -7290,7 +7294,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R83" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C84" type="list">
@@ -7310,7 +7314,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K84" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q84" type="list">
@@ -7318,7 +7322,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R84" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C85" type="list">
@@ -7338,7 +7342,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K85" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q85" type="list">
@@ -7346,7 +7350,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R85" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C86" type="list">
@@ -7366,7 +7370,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K86" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q86" type="list">
@@ -7374,7 +7378,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R86" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C87" type="list">
@@ -7394,7 +7398,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K87" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q87" type="list">
@@ -7402,7 +7406,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R87" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C88" type="list">
@@ -7422,7 +7426,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K88" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q88" type="list">
@@ -7430,7 +7434,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R88" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C89" type="list">
@@ -7450,7 +7454,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K89" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q89" type="list">
@@ -7458,7 +7462,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R89" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C90" type="list">
@@ -7478,7 +7482,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K90" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q90" type="list">
@@ -7486,7 +7490,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R90" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C91" type="list">
@@ -7506,7 +7510,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K91" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q91" type="list">
@@ -7514,7 +7518,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R91" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C92" type="list">
@@ -7534,7 +7538,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K92" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q92" type="list">
@@ -7542,7 +7546,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R92" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C93" type="list">
@@ -7562,7 +7566,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K93" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q93" type="list">
@@ -7570,7 +7574,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R93" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C94" type="list">
@@ -7590,7 +7594,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K94" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q94" type="list">
@@ -7598,7 +7602,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R94" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C95" type="list">
@@ -7618,7 +7622,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K95" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q95" type="list">
@@ -7626,7 +7630,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R95" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C96" type="list">
@@ -7646,7 +7650,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K96" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q96" type="list">
@@ -7654,7 +7658,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R96" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C97" type="list">
@@ -7674,7 +7678,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K97" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q97" type="list">
@@ -7682,7 +7686,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R97" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C98" type="list">
@@ -7702,7 +7706,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K98" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q98" type="list">
@@ -7710,7 +7714,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R98" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C99" type="list">
@@ -7730,7 +7734,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K99" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q99" type="list">
@@ -7738,7 +7742,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R99" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C100" type="list">
@@ -7758,7 +7762,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K100" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q100" type="list">
@@ -7766,7 +7770,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R100" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C101" type="list">
@@ -7786,7 +7790,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K101" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q101" type="list">
@@ -7794,7 +7798,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R101" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C102" type="list">
@@ -7814,7 +7818,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K102" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q102" type="list">
@@ -7822,7 +7826,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R102" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C103" type="list">
@@ -7842,7 +7846,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K103" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q103" type="list">
@@ -7850,7 +7854,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R103" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C104" type="list">
@@ -7870,7 +7874,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K104" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q104" type="list">
@@ -7878,7 +7882,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R104" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C105" type="list">
@@ -7898,7 +7902,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K105" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q105" type="list">
@@ -7906,7 +7910,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R105" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C106" type="list">
@@ -7926,7 +7930,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K106" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q106" type="list">
@@ -7934,7 +7938,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R106" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C107" type="list">
@@ -7954,7 +7958,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K107" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q107" type="list">
@@ -7962,7 +7966,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R107" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C108" type="list">
@@ -7982,7 +7986,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K108" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q108" type="list">
@@ -7990,7 +7994,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R108" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C109" type="list">
@@ -8010,7 +8014,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K109" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q109" type="list">
@@ -8018,7 +8022,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R109" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C110" type="list">
@@ -8038,7 +8042,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K110" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q110" type="list">
@@ -8046,7 +8050,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R110" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C111" type="list">
@@ -8066,7 +8070,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K111" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q111" type="list">
@@ -8074,7 +8078,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R111" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C112" type="list">
@@ -8094,7 +8098,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K112" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q112" type="list">
@@ -8102,7 +8106,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R112" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C113" type="list">
@@ -8122,7 +8126,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K113" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q113" type="list">
@@ -8130,7 +8134,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R113" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C114" type="list">
@@ -8150,7 +8154,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K114" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q114" type="list">
@@ -8158,7 +8162,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R114" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C115" type="list">
@@ -8178,7 +8182,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K115" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q115" type="list">
@@ -8186,7 +8190,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R115" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C116" type="list">
@@ -8206,7 +8210,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K116" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q116" type="list">
@@ -8214,7 +8218,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R116" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C117" type="list">
@@ -8234,7 +8238,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K117" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q117" type="list">
@@ -8242,7 +8246,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R117" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C118" type="list">
@@ -8262,7 +8266,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K118" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q118" type="list">
@@ -8270,7 +8274,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R118" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C119" type="list">
@@ -8290,7 +8294,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K119" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q119" type="list">
@@ -8298,7 +8302,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R119" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C120" type="list">
@@ -8318,7 +8322,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K120" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q120" type="list">
@@ -8326,7 +8330,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R120" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C121" type="list">
@@ -8346,7 +8350,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K121" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q121" type="list">
@@ -8354,7 +8358,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R121" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C122" type="list">
@@ -8374,7 +8378,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K122" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q122" type="list">
@@ -8382,7 +8386,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R122" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C123" type="list">
@@ -8402,7 +8406,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K123" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q123" type="list">
@@ -8410,7 +8414,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R123" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C124" type="list">
@@ -8430,7 +8434,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K124" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q124" type="list">
@@ -8438,7 +8442,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R124" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C125" type="list">
@@ -8458,7 +8462,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K125" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q125" type="list">
@@ -8466,7 +8470,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R125" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C126" type="list">
@@ -8486,7 +8490,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K126" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q126" type="list">
@@ -8494,7 +8498,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R126" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C127" type="list">
@@ -8514,7 +8518,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K127" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q127" type="list">
@@ -8522,7 +8526,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R127" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C128" type="list">
@@ -8542,7 +8546,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K128" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q128" type="list">
@@ -8550,7 +8554,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R128" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C129" type="list">
@@ -8570,7 +8574,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K129" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q129" type="list">
@@ -8578,7 +8582,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R129" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C130" type="list">
@@ -8598,7 +8602,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K130" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q130" type="list">
@@ -8606,7 +8610,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R130" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C131" type="list">
@@ -8626,7 +8630,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K131" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q131" type="list">
@@ -8634,7 +8638,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R131" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C132" type="list">
@@ -8654,7 +8658,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K132" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q132" type="list">
@@ -8662,7 +8666,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R132" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C133" type="list">
@@ -8682,7 +8686,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K133" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q133" type="list">
@@ -8690,7 +8694,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R133" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C134" type="list">
@@ -8710,7 +8714,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K134" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q134" type="list">
@@ -8718,7 +8722,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R134" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C135" type="list">
@@ -8738,7 +8742,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K135" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q135" type="list">
@@ -8746,7 +8750,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R135" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C136" type="list">
@@ -8766,7 +8770,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K136" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q136" type="list">
@@ -8774,7 +8778,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R136" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C137" type="list">
@@ -8794,7 +8798,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K137" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q137" type="list">
@@ -8802,7 +8806,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R137" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C138" type="list">
@@ -8822,7 +8826,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K138" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q138" type="list">
@@ -8830,7 +8834,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R138" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C139" type="list">
@@ -8850,7 +8854,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K139" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q139" type="list">
@@ -8858,7 +8862,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R139" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C140" type="list">
@@ -8878,7 +8882,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K140" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q140" type="list">
@@ -8886,7 +8890,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R140" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C141" type="list">
@@ -8906,7 +8910,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K141" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q141" type="list">
@@ -8914,7 +8918,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R141" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C142" type="list">
@@ -8934,7 +8938,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K142" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q142" type="list">
@@ -8942,7 +8946,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R142" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C143" type="list">
@@ -8962,7 +8966,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K143" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q143" type="list">
@@ -8970,7 +8974,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R143" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C144" type="list">
@@ -8990,7 +8994,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K144" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q144" type="list">
@@ -8998,7 +9002,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R144" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C145" type="list">
@@ -9018,7 +9022,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K145" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q145" type="list">
@@ -9026,7 +9030,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R145" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C146" type="list">
@@ -9046,7 +9050,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K146" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q146" type="list">
@@ -9054,7 +9058,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R146" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C147" type="list">
@@ -9074,7 +9078,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K147" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q147" type="list">
@@ -9082,7 +9086,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R147" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C148" type="list">
@@ -9102,7 +9106,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K148" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q148" type="list">
@@ -9110,7 +9114,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R148" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C149" type="list">
@@ -9130,7 +9134,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K149" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q149" type="list">
@@ -9138,7 +9142,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R149" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C150" type="list">
@@ -9158,7 +9162,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K150" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q150" type="list">
@@ -9166,7 +9170,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R150" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C151" type="list">
@@ -9186,7 +9190,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K151" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q151" type="list">
@@ -9194,7 +9198,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R151" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C152" type="list">
@@ -9214,7 +9218,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K152" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q152" type="list">
@@ -9222,7 +9226,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R152" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C153" type="list">
@@ -9242,7 +9246,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K153" type="list">
-      <formula1>"Não testada,Testada — inefetiva,Testada — parcialmente efetiva,Testada — efetiva,Não aplicável"</formula1>
+      <formula1>"Não testada,Testada: inefetiva,Testada: parcialmente efetiva,Testada: efetiva,Não aplicável"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q153" type="list">
@@ -9250,10 +9254,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Valor fora da lista permitida. Escolha um dos itens do menu suspenso." errorStyle="stop" errorTitle="Entrada inválida" operator="between" prompt="Escolha um valor da lista." promptTitle="Selecione" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R153" type="list">
-      <formula1>"Não,Sim — nova evidência,Sim — mudança de escopo,Sim — falha identificada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: CHK-001." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão CHK-001. Não é gerado automaticamente — preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A153" type="custom">
+      <formula1>"Não,Sim: nova evidência,Sim: mudança de escopo,Sim: falha identificada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Este identificador já existe nesta coluna. Cada ID deve ser único e estável (não reutilize nem renumere IDs já atribuídos). Padrão esperado: CHK-001." errorStyle="stop" errorTitle="ID duplicado" operator="between" prompt="Digite um identificador único e estável, padrão CHK-001. Não é gerado automaticamente; preserve o mesmo ID após inserir, excluir ou reordenar linhas." promptTitle="Identificador manual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A4:A153" type="custom">
       <formula1>OR(A4="",COUNTIF($A$4:$A$153,A4)&lt;=1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
